--- a/5_evaluation_results/pairwise_similarity_results_v2/FINAL_3categories_similarity_and_performance/category_profile_summary_table.xlsx
+++ b/5_evaluation_results/pairwise_similarity_results_v2/FINAL_3categories_similarity_and_performance/category_profile_summary_table.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Qwen3.8-9B-think-temp1, ministral3-14B, Nemotron3-Nano-30B-A3B, Qwen3-Next-80B-A3B-Instruct, gemma-4-12B-it, gemma-4-31B-it</t>
+          <t>Qwen3.5-9B-think-temp1, ministral3-14B, Nemotron3-Nano-30B-A3B, Qwen3-Next-80B-A3B-Instruct, gemma-4-12B-it, gemma-4-31B-it</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
